--- a/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
+++ b/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,11 +43,8 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002F7D5B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="002F7D5B"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -99,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,8 +133,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,17 +498,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,7 +570,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/05/05</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -585,11 +580,11 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>アクセスチケット 大阪駅前第2ビル店</t>
+          <t>JR西日本 大津京駅</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>4980</v>
+        <v>5000</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -600,118 +595,126 @@
         <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局 東山</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>アクセスチケット 大阪駅前第2ビル店</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>4980</v>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>金券：阪急阪神優待@385×4＋京阪乗車券@430×8。登録番号1021001018755</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/07</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>421.36</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>4213.64</v>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>楽天市場（セブン払込・イーザッコ米）</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>5670</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>品目不明のため科目仮置き。米（食品）なら軽減8%の可能性→要確認</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4980</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>金券：阪急阪神優待@385×4＋京阪乗車券@430×8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Amazon（セブン払込）</t>
+          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>7590</v>
+        <v>4635</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>421.36</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>4213.64</v>
+      </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>品目不明のため科目仮置き→要確認</t>
+          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -721,11 +724,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>浜大津酒場（大津）</t>
+          <t>居酒屋ひがも（京都市山科区）</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2590</v>
+        <v>5180</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -733,35 +736,35 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>235.45</v>
+        <v>470.91</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2354.55</v>
+        <v>4709.09</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>但 飲食代として</t>
+          <t>飲食代 ※内消費税額の記載なし・概算</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>荷造運賃</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ヤマト運輸（宛：堺市 ㈱MIZUKEN環境分析センター）</t>
+          <t>串かつ屋 まねき串（京都市山科区）</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1530</v>
+        <v>5100</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -769,304 +772,745 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>139.09</v>
+        <v>464</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1390.91</v>
+        <v>4636</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>宅急便 送り状。土壌分析関連の発送と推定</t>
+          <t>ご飲食代</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026/05/(要確認)</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>大阪信用金庫（ATM）</t>
+          <t>楽天市場（セブン払込・イーザッコ米）</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>110</v>
+        <v>5670</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>100</v>
-      </c>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
+          <t>品目不明→科目仮。米（食品）なら軽減8%の可能性</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/06 ──</t>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Amazon（セブン払込）</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>7590</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道（浜大津・手書き）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>会議費・接待費</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4048</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>浜大津酒場（大津）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>課税（内税10%）</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>368</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>3680</v>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>飲食2名。登録番号 T9040001029191</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Agoda（M's Hotel 三条 和国）</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>25428</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>要確認（海外OTA）</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
+      <c r="F13" s="6" t="n">
+        <v>235.45</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2354.55</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>但 飲食代として</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>── 参考：資金移動（経費対象外） ──</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>京都紫明ライオンズクラブ</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>大文字登山アクティビティ 会費として</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>荷造運賃</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ヤマト運輸（宛：堺市 ㈱MIZUKEN環境分析センター）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1390.91</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>宅急便 送り状</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026/05/(要確認)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>大阪信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/06 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/07</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/07</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 浜大津四丁目店</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>プリント代</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 梅田ダイヒル店</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>870</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>791</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>飲食（クレジット）。登録番号1413001010267</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>大阪メトロ 谷町九丁目駅</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>（店名判読不可）お買上票</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>7480</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>6800</v>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>品目・店名不明→科目仮。登録番号T5120001224663</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 横浜スカイビル店</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>プリント代</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>東急電鉄 大井町駅</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>現金チャージ。登録番号T2011001127829</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>368</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>3680</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>飲食2名。登録番号T9040001029191</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Agoda（M's Hotel 三条 和国）</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>25428</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>要確認（海外OTA）</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>── 参考：資金移動（経費対象外） ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>（資金移動・対象外）</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>PayPay銀行 ATM</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>残高36,412／ATM手数料0。経費ではない</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>残高36,412／ATM手数料0。経費でない</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>2026/05/(要確認)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>（資金移動・対象外）</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>大阪信用金庫 ATM 引出</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D29" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>現金引出＝普通預金→現金。経費でない（手数料110は上に計上）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>経費 合計（要確認分を含む・暫定）</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
-        <v>56581</v>
-      </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="D30" s="14" t="n">
+        <v>92431</v>
+      </c>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>※黄色＝要確認。ATM引出¥50,000は合計に含めない</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" s="15" t="inlineStr">
+    <row r="32">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>科目別小計</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
+    <row r="33">
+      <c r="C33" t="inlineStr">
         <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
-        <v>30408</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>アクセスチケット＋Agoda宿泊</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
+      <c r="D33" s="16" t="n">
+        <v>45408</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
         <is>
           <t>会議費・接待費</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
-        <v>11273</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>マルリキ＋浜大津＋Grill&amp;Bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>消耗品費(仮)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>13260</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>楽天＋Amazon（品目要確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
+      <c r="D34" s="16" t="n">
+        <v>22423</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>20960</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
         <is>
           <t>荷造運賃</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D37" s="16" t="n">
         <v>1530</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ヤマト送料</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D38" s="16" t="n">
         <v>110</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>ATM手数料</t>
-        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1079,324 +1523,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>② 山中俊成フォルダで、写真がぼやける等でOCRできなかったレシートです。どれか分かるようファイル名とリンクを記載しました。</t>
+          <t>② 山中俊成フォルダの写真：2026-07-20の再読込で【全14枚 判読完了】。現在、読取不能はありません。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>ファイル名</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>Google Drive リンク</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>バッチ</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>1781283398021.jpg</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1YRTt6izI8LzBSOSI4PQ9ATmqXrXsHkm5/view</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>・1781283397994.jpg と 1781283365409.jpg は同一（居酒屋ひがも 5/9 ¥5,180）。1件として計上。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>1781283398019.jpg</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1AM656pwP6Lnc4UI8UJXLK6M05brFnbcd/view</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>1781283398018.jpg</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1CEGobY0wH_ZYiEE6FYb9bHKOXjXK2PiI/view</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>1781283398008.jpg</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/13415QcJmD1TOHxPcLq5ocP71h7mOalvI/view</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>1781283398005.jpg</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1f9LEvvOc67qSXlH3S13yNIA8cdJIADox/view</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>1781283398017.jpg</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1QgZCpVCsKqI8Xw5psJnsPNCocrooU0FB/view</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>1781283398015.jpg</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/14SkBigjlf_oXe4wyV0o9B3zCdFvRCEYL/view</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>1781283398000.jpg</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ovB6w3Tap6DhjOmi4C1QZwp2WnRNDR9f/view</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>1781283397996.jpg</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1JjJH4IoGE3TI6IhkXidE-khcYngzELu9/view</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>1781283397994.jpg</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1tikA0d1HWcSFSz_gdo0-_F2cSG0_aDJY/view</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>365409と同一の可能性</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>1781283365409.jpg</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1RkhZxszRE4W9pJFD45vMIc4EG2LoG1WT/view</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>397994と同一の可能性</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>1781283365407.jpg</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1CcOzM4RwePl8_qYhSEMNOiUfweecNpN4/view</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>1781283365365.jpg</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Cd-3P6oxWfmcR1XcmYmp2CemTHx7j4j6/view</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>1781283365362.jpg</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/15n2GDVrJm9vVEu2broknRWtaifeR-Cug/view</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>・当初OCRで空だった写真も、画像を直接取り込む方式で全て判読しました。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId14"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
+++ b/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="経費帳簿（統合）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="読取不能（要再撮影）" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,11 +39,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="002F7D5B"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -96,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,9 +103,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -121,18 +112,12 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>経費帳簿　②（2026年4月1日〜）　立替：山中俊成　※①(2025/7-2026/3)は決算済・別ファイル</t>
+          <t>経費帳簿　②（2026年4月1日〜）　立替：山中俊成　※フォルダ内レシート写真を全反映（重複除去済）／①(2025/7-2026/3)は決算済・別</t>
         </is>
       </c>
     </row>
@@ -563,158 +548,100 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>── 2026/05 ──</t>
+          <t>── 2025/07 ──</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/05</t>
+          <t>2025/07/16</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大津京駅</t>
+          <t>Swissotel Nankai Osaka（Swiss Gourmet）</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T3120001104504</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/06</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>京都市交通局 東山</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>── 2025/12 ──</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>アクセスチケット 大阪駅前第2ビル店</t>
+          <t>CAFE 英國屋 阪急17番街店</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4980</v>
+        <v>2730</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>金券：阪急阪神優待@385×4＋京阪乗車券@430×8</t>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2482</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>飲食（カフェ）／登録番号T8120001080641</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/07</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>421.36</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>4213.64</v>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/02 ──</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/02/20</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -724,133 +651,112 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>居酒屋ひがも（京都市山科区）</t>
+          <t>あびこハウス</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5180</v>
+        <v>1400</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>課税（内税10%）</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>470.91</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>4709.09</v>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>飲食代 ※内消費税額の記載なし・概算</t>
+      <c r="F8" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T3120001032416</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>串かつ屋 まねき串（京都市山科区）</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>464</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>4636</v>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>ご飲食代</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/04 ──</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>楽天市場（セブン払込・イーザッコ米）</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>5670</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮。米（食品）なら軽減8%の可能性</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>JR東海 京都駅</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>12650</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>11500</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>JR乗車券類。登録番号T3180001031569</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Amazon（セブン払込）</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>7590</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>JR東海リテイリング（京都土産・プレシャスデリ）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4104</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>辻利の里/ぎおんの里 他3点（手土産）。登録番号T8180001031531</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/04/01</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -860,33 +766,33 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>京阪電気鉄道（浜大津・手書き）</t>
+          <t>京都市交通局</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>非課税</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="G12" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金／登録番号T8800020000809</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -896,252 +802,285 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>浜大津酒場（大津）</t>
+          <t>すしめん処 大京 そめい野店</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2590</v>
+        <v>3401</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>課税（内税10%）</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>235.45</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>2354.55</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>但 飲食代として</t>
+      <c r="F13" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3092</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1040001082173</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>諸会費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>京都紫明ライオンズクラブ</t>
+          <t>まり花 大井町</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2000</v>
+        <v>6940</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>大文字登山アクティビティ 会費として</t>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>631</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6309</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>飲食（PayPay）／登録番号T8010701023860</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>荷造運賃</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ヤマト運輸（宛：堺市 ㈱MIZUKEN環境分析センター）</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1530</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>139.09</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1390.91</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>宅急便 送り状</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>千代田・染井野ふれあいセンター</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>1318</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>第三会議室利用料／税額印字なし・推定</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026/05/(要確認)</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>大阪信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>炉端のいろ葉</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8320</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>756</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7564</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T2010001128936</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/06 ──</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>東急電鉄 青葉台駅</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/04/03</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+          <t>デリーモ東京カフェ 大丸東京店</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1000</v>
+        <v>1694</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1011001046533</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/04/03</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>川崎市中原市民館</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1119</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>第4会議室利用料／登録番号T3011501000765</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>消耗品費</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>ローソン 浜大津四丁目店</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>164</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>プリント代</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Holly's Café 梅田ダイヒル店</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>870</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>791</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>飲食（クレジット）。登録番号1413001010267</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>foodium武蔵小杉</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮／登録番号T3040001015833</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1151,416 +1090,4478 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>大阪メトロ 谷町九丁目駅</t>
+          <t>JR西日本 新大阪駅</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>非課税</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>（店名判読不可）お買上票</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>7480</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>680</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>6800</v>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>品目・店名不明→科目仮。登録番号T5120001224663</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/04</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>JR東日本 長津田駅</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>12650</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>12650</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>JR乗車券類／登録番号T7011001029587</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ローソン 横浜スカイビル店</t>
+          <t>大阪メトロ 難波駅</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>プリント代</t>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>東急電鉄 大井町駅</t>
+          <t>ガスト なんば店</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1000</v>
+        <v>1786</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>現金チャージ。登録番号T2011001127829</t>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1624</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T2012401030556</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/04/08</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
+          <t>日本郵便（京都知恩院前郵便局）</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4048</v>
+        <v>11500</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>368</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>3680</v>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>飲食2名。登録番号T9040001029191</t>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>11500</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>レターパック・切手（金券・非課税）／登録番号T1010001112577</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/09</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>浪速日本橋食堂</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1573</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1120001010547</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/09</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Agoda（M's Hotel 三条 和国）</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>25428</v>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>要確認（海外OTA）</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>── 参考：資金移動（経費対象外） ──</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>（資金移動・対象外）</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>PayPay銀行 ATM</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n"/>
+          <t>大阪メトロ 谷町四丁目駅</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5000</v>
+      </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>残高36,412／ATM手数料0。経費でない</t>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 大阪駅前第1ビル店</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 大阪駅前第1ビル店</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>545</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>屯舎喜酔（Kissui）</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>5412</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>492</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>4920</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／税額印字なし・推定／登録番号T9120001173948</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>JR東海 京都駅</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>JR乗車券類／登録番号T3180001031569</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/12</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>ワークマン女子 イオンモールKYOTO店</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3480</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>3164</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>作業着／登録番号T1070001013828</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PRONTO 中之島フェスティバルプラザ店</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>792</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T1801040102651</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>株式会社ヨネヤ商店（なんばウォーク）</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>5315</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>5315</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮／税額印字なし／登録番号T2120001071828</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 祇園四条駅</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/18</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 三国ケ丘駅</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>大阪メトロ 大阪港駅</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/21</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>JR東海 京都駅</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>JR乗車券類2枚／登録番号T3180001031569</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>貴船コスメティックス&amp;ギャラリー</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>株式会社紀州プラットフォーム</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>909</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>会議費として／税額印字なし・推定</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>太郎屋（京都市中京区）</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>5430</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>493</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>4937</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1130002002609</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>KIFUNE COSMETICS &amp; GALLERY</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1046</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T3130001005973</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>イノダコーヒ ポルタ支店</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1955</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T2130001019883</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>ラーメン魅力屋 河原町三条店</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>4202</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>3820</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T7130001075864</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/23</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>551蓬莱 ポルタ京都店</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>899</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>タリーズコーヒー 祇園花見小路店</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T9011101048118</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金／登録番号T8800020000809</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/26</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>京都伝統産業ミュージアムショップ</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>誰が袖（衣装用・匂い袋）／登録番号T5130001007704</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>保険料</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>東京海上日動火災保険</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>12100</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>12100</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>保険料（コンビニ払込）・非課税</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/29</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>すき家 浜大津店</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>973</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>飲食／深夜料70含む／登録番号T2010401093920</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/29</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>GION GOZU（祇園）</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1908</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>お土産（菓子）／手提げ袋のみ10%／登録番号T5160001021611</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/29</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>ワークマン女子 イオンモールKYOTO店</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3480</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>3164</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>作業着／登録番号T1070001013828</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>日本郵便（大津観音寺郵便局）</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>スマートレター（郵便・非課税）／登録番号T1010001112577</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/05 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>株式会社アルテピアノ</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>業務費として／税額印字なし・科目仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>スターバックス なんば御堂筋グランドビル店</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>440</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T7011001031943</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>大衆そば酒場 しのぶ庵 新大阪店</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>7436</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>676</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>6760</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T8120002069808</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>スターバックス なんば御堂筋グランドビル店</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T7011001031943</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/02</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>中華料理 麒麟（大阪市中央区）</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>10540</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>958</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>9582</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>飲食（中華）／税額印字なし・推定／登録番号T8810205792540</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大津京駅</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>パンとエスプレッソと嵐山庭園</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>2930</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2714</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>パン・軽食（8%中心／袋のみ10%）／登録番号T4120001146446</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局 東山</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>DCM 川内店</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>2777</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>2525</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>ゴム板・ネジロックカッター／登録番号T7010701039115</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>竈 炊き立てごはん 土井 八条口店</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T8130001006884</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>アクセスチケット 大阪2ビル店</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>4980</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>4980</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>金券（阪急阪神優待カード・京阪乗車券）／登録番号T1021001018755</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>421</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>4213</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>3259</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>居酒屋ひがも（京都市山科区）</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>5180</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>4709</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>飲食代 ※内消費税額の記載なし・概算</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>串かつ屋 まねき串（京都市山科区）</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>464</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>4636</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>ご飲食代</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>楽天市場（セブン払込・イーザッコ米）</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>5670</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮。米（食品）なら軽減8%の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Amazon（セブン払込）</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>7590</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>amazon（コンビニ払込・ウェルネット）</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>7590</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>7590</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮／インボイスなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道（浜大津・手書き）</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>浜大津酒場（大津）</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>2354</v>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>但 飲食代として</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>京都紫明ライオンズクラブ</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>大文字登山アクティビティ 会費として</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Agoda（Y's Cabin Osaka Namba）</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>要確認（海外OTA）</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>1882</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>宿泊1泊／USD11.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>はちきん（新梅田食道街）</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>11540</v>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>1049</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>10491</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／登録番号T5122001015976</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>ペレ・グレイス（宅急便コレクト・代引）</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税）</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>2736</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>29264</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>品目：美容液・サプリ・書籍／科目仮・要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/16</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>雑費</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>PLAGE BARBER SHOP 山科店</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>散髪代（カット）・経費該当要確認／登録番号T7120101032980</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/17</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金／登録番号T8800020000809</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>遠京茶寮</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>354</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>3546</v>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T1400001155689</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>あびこハウス</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1364</v>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T3120001032416</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大津京駅</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 堺筋本町店</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>1309</v>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 大津中央二丁目店</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>交通系マネーチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>株式会社串まつ屋</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>9020</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>820</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>8200</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>飲食（串カツ）／税額印字なし・推定／登録番号T5120001224663</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>阪急電鉄 大阪梅田駅</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>デリカフェ・キッチン大阪</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>1064</v>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T6120001064803</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 京都駅</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>阪急梅田 2階中央催事</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>交通系IC支払・品目不明→科目仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>南海 新今宮駅店（交通系IC支払）</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>740</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>740</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>梅田大衆酒場H</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>2118</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>1926</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／登録番号T3120001194454</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>東北うまいもの祭り 阪急梅田店（新杵屋）</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>2090</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>1936</v>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>お土産（食品）／登録番号T8390002012939</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>どんがめ 大阪駅前第二ビル店</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>3443</v>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>313</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>3130</v>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T4120001220630</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>ZETTERIA ディアモール大阪</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>593</v>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>飲食（テイクアウト）／登録番号T6011101058111</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>551蓬莱 南海新今宮店</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>686</v>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>荷造運賃</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>ヤマト運輸（宅急便着払）</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>宅急便着払・精密機器（MIZUKENより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>アクセスチケット 大阪2ビル店</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>金券（阪急阪神優待カード10回）／登録番号T1021001018755</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>サイゼリヤ 大阪駅前第3ビル</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>637</v>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T8030001065552</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>インド家庭料理 マハラジャ</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>4439</v>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="G106" s="8" t="n">
+        <v>4035</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>飲食／税額印字なし・推定／登録番号T6120102023261</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>京田辺三山木食堂</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>2950</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T2150003002514</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>京都 舞妓の茶本舗</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>課税（外税8%）</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>お茶（徳用ティーバッグ・軽減8%）／登録番号T3130001069770</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>コンセプト JR三山木駅前第2パーキング</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>駐車場代／登録番号T2130001023547</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 墨染駅</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/06 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>甘党 御座候（西中島）</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>お土産（御座候・食品）／登録番号T1140001058816</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>タリーズコーヒー 新大阪阪急ビル店</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T9011101048118</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 新大阪駅</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大津駅</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>セブンイレブン ハートインJR大阪駅西店</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>プリント代／登録番号T6140001055008</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>セブンイレブン ハートインJR大阪駅西店</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>プリント代／登録番号T6140001055008</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>スターバックス エキマルシェ大阪店</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>394</v>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>交通系IC伝票（同一取引）／登録番号T7011001031943</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/04</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>でんがな 大阪駅前第2ビル店</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>3931</v>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>357</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／登録番号T1010401049915</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>酒場 おちょぼ 大阪駅前第3ビル店</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／登録番号T2120001110726</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/07</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/07</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 浜大津四丁目店</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>プリント代</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 梅田ダイヒル店</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>870</v>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>791</v>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>飲食（クレジット）。登録番号1413001010267</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>大阪メトロ 谷町九丁目駅</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>（店名判読不可）お買上票</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>7480</v>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>680</v>
+      </c>
+      <c r="G126" s="8" t="n">
+        <v>6800</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>品目・店名不明→科目仮。登録番号T5120001224663</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 横浜スカイビル店</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>プリント代</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>東急電鉄 大井町駅</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>現金チャージ。登録番号T2011001127829</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>3680</v>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>飲食2名。登録番号T9040001029191</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>山下本気うどん 横浜ポルタ</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>991</v>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1011101075301</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>大津ハイウエイレストラン（大津SA・GRANVISTA）</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>2298</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%/10%）</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2119</v>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>お土産（ちりめん山椒・菓子）／登録番号T2010001093115</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>atré品川（JRE POINT明細）</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="8" t="n">
+        <v>4048</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>ポイント明細票・税額印字なし（AW5-5アトレ品川と同一取引の可能性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 京都駅</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/10</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>らーめん小菜 古潭 サン広場店</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>343</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>3437</v>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>飲食（ラーメン）／登録番号T8120001071814</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Agoda（M's Hotel 三条 和国）</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>25428</v>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>要確認（海外OTA）</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="n"/>
+      <c r="G135" s="7" t="n"/>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/05 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
           <t>2026/05/(要確認)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>大阪信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>── 参考：資金移動（経費対象外） ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/09</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>（資金移動・対象外）</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>楽天銀行（ATM）</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>ATM・金額印字なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外／手数料110円</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>PayPay銀行 ATM</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>残高36,412／ATM手数料0。経費でない</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>大阪信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外／手数料110円</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>PayPay銀行（ATM）</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>残高照会・金額印字なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外／手数料110円</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/(要確認)</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>大阪信用金庫 ATM 引出</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D146" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="6" t="inlineStr">
         <is>
           <t>現金引出＝普通預金→現金。経費でない（手数料110は上に計上）</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="13" t="inlineStr">
+    <row r="148">
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>経費 合計（要確認分を含む・暫定）</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>92431</v>
-      </c>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>※黄色＝要確認。ATM引出¥50,000は合計に含めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="15" t="inlineStr">
+      <c r="D148" s="11" t="n">
+        <v>482983</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>明細128件（重複除去済）／黄色＝要確認。ATM引出等は合計に含めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>科目別小計</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
+    <row r="151">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="n">
+        <v>181908</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" t="inlineStr">
         <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="D33" s="16" t="n">
-        <v>45408</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>22423</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
+      <c r="D152" s="12" t="n">
+        <v>177490</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" t="inlineStr">
         <is>
           <t>消耗品費</t>
         </is>
       </c>
-      <c r="D35" s="16" t="n">
-        <v>20960</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
+      <c r="D153" s="12" t="n">
+        <v>93935</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>保険料</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="n">
+        <v>11710</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>雑費</t>
+        </is>
+      </c>
+      <c r="D156" s="12" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="C157" t="inlineStr">
         <is>
           <t>諸会費</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D157" s="12" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
+    <row r="158">
+      <c r="C158" t="inlineStr">
         <is>
           <t>荷造運賃</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D158" s="12" t="n">
         <v>1530</v>
       </c>
     </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
+    <row r="159">
+      <c r="C159" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D159" s="12" t="n">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A27:H27"/>
+  <mergeCells count="9">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>② 山中俊成フォルダの写真：2026-07-20の再読込で【全14枚 判読完了】。現在、読取不能はありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>メモ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>・1781283397994.jpg と 1781283365409.jpg は同一（居酒屋ひがも 5/9 ¥5,180）。1件として計上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>・当初OCRで空だった写真も、画像を直接取り込む方式で全て判読しました。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A136:H136"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A138:H138"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A111:H111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
+++ b/company/secretary/経理/経費帳簿/立替_山中_期間2_2026年4月〜.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -493,13 +493,13 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>経費帳簿　②（2026年4月1日〜）　立替：山中俊成　※フォルダ内レシート写真を全反映（重複除去済）／①(2025/7-2026/3)は決算済・別</t>
+          <t>経費帳簿　②（2026年4月1日〜）　立替：山中俊成　※②フォルダ内レシート全反映・重複/期間外除去済／①は決算済・別</t>
         </is>
       </c>
     </row>
@@ -548,28 +548,28 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>── 2025/07 ──</t>
+          <t>── 2026/04 ──</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2025/07/16</t>
+          <t>2026/04/01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Swissotel Nankai Osaka（Swiss Gourmet）</t>
+          <t>JR東海 京都駅</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1400</v>
+        <v>12650</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -577,71 +577,129 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>127</v>
+        <v>1150</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1273</v>
+        <v>11500</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T3120001104504</t>
+          <t>JR乗車券類。登録番号T3180001031569</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>── 2025/12 ──</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>JR東海リテイリング（京都土産・プレシャスデリ）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>4104</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>辻利の里/ぎおんの里 他3点（手土産）。登録番号T8180001031531</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2025/12/15</t>
+          <t>2026/04/01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CAFE 英國屋 阪急17番街店</t>
+          <t>京都市交通局</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2730</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2482</v>
+        <v>5000</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>飲食（カフェ）／登録番号T8120001080641</t>
+          <t>ICカード入金／登録番号T8800020000809</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/02 ──</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>すしめん処 大京 そめい野店</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3401</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>3092</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1040001082173</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026/02/20</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -651,11 +709,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>あびこハウス</t>
+          <t>まり花 大井町</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1400</v>
+        <v>6940</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -663,42 +721,71 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>127</v>
+        <v>631</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1273</v>
+        <v>6309</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T3120001032416</t>
+          <t>飲食（PayPay）／登録番号T8010701023860</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/04 ──</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/02</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>千代田・染井野ふれあいセンター</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1318</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>第三会議室利用料／税額印字なし・推定</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026/04/01</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>JR東海 京都駅</t>
+          <t>炉端のいろ葉</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>12650</v>
+        <v>8320</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -706,93 +793,93 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1150</v>
+        <v>756</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>11500</v>
+        <v>7564</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>JR乗車券類。登録番号T3180001031569</t>
+          <t>飲食／登録番号T2010001128936</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026/04/01</t>
+          <t>2026/04/03</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>JR東海リテイリング（京都土産・プレシャスデリ）</t>
+          <t>東急電鉄 青葉台駅</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4104</v>
+        <v>5000</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3800</v>
+        <v>5000</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>辻利の里/ぎおんの里 他3点（手土産）。登録番号T8180001031531</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026/04/01</t>
+          <t>2026/04/03</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>京都市交通局</t>
+          <t>デリーモ東京カフェ 大丸東京店</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5000</v>
+        <v>1694</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5000</v>
+        <v>1540</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>ICカード入金／登録番号T8800020000809</t>
+          <t>飲食／登録番号T1011001046533</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026/04/02</t>
+          <t>2026/04/03</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -802,11 +889,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>すしめん処 大京 そめい野店</t>
+          <t>川崎市中原市民館</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3401</v>
+        <v>1230</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -814,129 +901,129 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>309</v>
+        <v>111</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>3092</v>
+        <v>1119</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T1040001082173</t>
+          <t>第4会議室利用料／登録番号T3011501000765</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/02</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>まり花 大井町</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>6940</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>631</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>6309</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>飲食（PayPay）／登録番号T8010701023860</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>foodium武蔵小杉</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮／登録番号T3040001015833</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/02</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>千代田・染井野ふれあいセンター</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>132</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>1318</v>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>第三会議室利用料／税額印字なし・推定</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/04</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 新大阪駅</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026/04/02</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>炉端のいろ葉</t>
+          <t>JR東日本 長津田駅</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>8320</v>
+        <v>12650</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>7564</v>
+        <v>12650</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T2010001128936</t>
+          <t>JR乗車券類／登録番号T7011001029587</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026/04/03</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -946,11 +1033,11 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>東急電鉄 青葉台駅</t>
+          <t>大阪メトロ 難波駅</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -961,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -972,7 +1059,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026/04/03</t>
+          <t>2026/04/04</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -982,11 +1069,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>デリーモ東京カフェ 大丸東京店</t>
+          <t>ガスト なんば店</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1694</v>
+        <v>1786</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -994,93 +1081,93 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1540</v>
+        <v>1624</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T1011001046533</t>
+          <t>飲食／登録番号T2012401030556</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026/04/03</t>
+          <t>2026/04/08</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>川崎市中原市民館</t>
+          <t>日本郵便（京都知恩院前郵便局）</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1230</v>
+        <v>11500</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1119</v>
+        <v>11500</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>第4会議室利用料／登録番号T3011501000765</t>
+          <t>レターパック・切手（金券・非課税）／登録番号T1010001112577</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/03</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>foodium武蔵小杉</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>217</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>課税（外税10%）</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>198</v>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮／登録番号T3040001015833</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/09</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>浪速日本橋食堂</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1573</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1120001010547</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1090,11 +1177,11 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 新大阪駅</t>
+          <t>JR西日本 大阪駅</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1105,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1116,7 +1203,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1126,11 +1213,11 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>JR東日本 長津田駅</t>
+          <t>大阪メトロ 谷町四丁目駅</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>12650</v>
+        <v>5000</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -1141,54 +1228,54 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>12650</v>
+        <v>5000</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>JR乗車券類／登録番号T7011001029587</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>大阪メトロ 難波駅</t>
+          <t>Holly's Café 大阪駅前第1ビル店</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026/04/04</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1198,11 +1285,11 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>ガスト なんば店</t>
+          <t>Holly's Café 大阪駅前第1ビル店</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1786</v>
+        <v>600</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -1210,273 +1297,273 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1624</v>
+        <v>545</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T2012401030556</t>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/08</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>日本郵便（京都知恩院前郵便局）</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>11500</v>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>11500</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>レターパック・切手（金券・非課税）／登録番号T1010001112577</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/10</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>屯舎喜酔（Kissui）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>5412</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>492</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>4920</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／税額印字なし・推定／登録番号T9120001173948</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/10</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>浪速日本橋食堂</t>
+          <t>JR東海 京都駅</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1730</v>
+        <v>1450</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1573</v>
+        <v>1450</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T1120001010547</t>
+          <t>JR乗車券類／登録番号T3180001031569</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/12</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大阪駅</t>
+          <t>ワークマン女子 イオンモールKYOTO店</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1000</v>
+        <v>3480</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1000</v>
+        <v>3164</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>作業着／登録番号T1070001013828</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>大阪メトロ 谷町四丁目駅</t>
+          <t>PRONTO 中之島フェスティバルプラザ店</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>5000</v>
+        <v>792</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T1801040102651</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>株式会社ヨネヤ商店（なんばウォーク）</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>5315</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/10</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Holly's Café 大阪駅前第1ビル店</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>飲食（カフェ）／登録番号T4130001010287</t>
+      <c r="G29" s="8" t="n">
+        <v>5315</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮／税額印字なし／登録番号T2120001071828</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Holly's Café 大阪駅前第1ビル店</t>
+          <t>京阪電気鉄道 祇園四条駅</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>545</v>
+        <v>10000</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>飲食（カフェ）／登録番号T4130001010287</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/10</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>屯舎喜酔（Kissui）</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>5412</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>492</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>4920</v>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>飲食（居酒屋）／税額印字なし・推定／登録番号T9120001173948</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/18</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 三国ケ丘駅</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/04/21</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1486,11 +1573,11 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>JR東海 京都駅</t>
+          <t>大阪メトロ 大阪港駅</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1450</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1501,414 +1588,414 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1450</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>JR乗車券類／登録番号T3180001031569</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026/04/12</t>
+          <t>2026/04/21</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ワークマン女子 イオンモールKYOTO店</t>
+          <t>JR東海 京都駅</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>3480</v>
+        <v>1450</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>3164</v>
+        <v>1450</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>作業着／登録番号T1070001013828</t>
+          <t>JR乗車券類2枚／登録番号T3180001031569</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>PRONTO 中之島フェスティバルプラザ店</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>792</v>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>飲食（コーヒー）／登録番号T1801040102651</t>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>株式会社紀州プラットフォーム</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>909</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>会議費として／税額印字なし・推定</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>株式会社ヨネヤ商店（なんばウォーク）</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>5315</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>5315</v>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮／税額印字なし／登録番号T2120001071828</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/22</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>太郎屋（京都市中京区）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>5430</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>493</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>4937</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T1130002002609</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/04/22</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>京阪電気鉄道 祇園四条駅</t>
+          <t>KIFUNE COSMETICS &amp; GALLERY</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>10000</v>
+        <v>1150</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>10000</v>
+        <v>1046</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（コーヒー）／登録番号T3130001005973</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026/04/18</t>
+          <t>2026/04/23</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 三国ケ丘駅</t>
+          <t>イノダコーヒ ポルタ支店</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2000</v>
+        <v>2150</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2000</v>
+        <v>1955</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（コーヒー）／登録番号T2130001019883</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026/04/21</t>
+          <t>2026/04/23</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>大阪メトロ 大阪港駅</t>
+          <t>ラーメン魅力屋 河原町三条店</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>5000</v>
+        <v>4202</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>5000</v>
+        <v>3820</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食／登録番号T7130001075864</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026/04/21</t>
+          <t>2026/04/23</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>551蓬莱 ポルタ京都店</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>899</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>タリーズコーヒー 祇園花見小路店</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>飲食（コーヒー）／登録番号T9011101048118</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>JR東海 京都駅</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>非課税</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>1450</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>JR乗車券類2枚／登録番号T3180001031569</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>貴船コスメティックス&amp;ギャラリー</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>1150</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>2026/04/22</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>株式会社紀州プラットフォーム</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>909</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>会議費として／税額印字なし・推定</t>
+      <c r="G41" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金／登録番号T8800020000809</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026/04/22</t>
+          <t>2026/04/26</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>太郎屋（京都市中京区）</t>
+          <t>京都伝統産業ミュージアムショップ</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>5430</v>
+        <v>1056</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>課税（外税10%）</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>493</v>
+        <v>96</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>4937</v>
+        <v>960</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T1130002002609</t>
+          <t>誰が袖（衣装用・匂い袋）／登録番号T5130001007704</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026/04/22</t>
+          <t>2026/04/27</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>KIFUNE COSMETICS &amp; GALLERY</t>
+          <t>東京海上日動火災保険</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1150</v>
+        <v>12100</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>対象外</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1046</v>
+        <v>12100</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T3130001005973</t>
+          <t>保険料（コンビニ払込）・非課税</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026/04/23</t>
+          <t>2026/04/29</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -1918,11 +2005,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>イノダコーヒ ポルタ支店</t>
+          <t>すき家 浜大津店</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2150</v>
+        <v>1070</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -1930,21 +2017,21 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1955</v>
+        <v>973</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T2130001019883</t>
+          <t>飲食／深夜料70含む／登録番号T2010401093920</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026/04/23</t>
+          <t>2026/04/29</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -1954,213 +2041,184 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ラーメン魅力屋 河原町三条店</t>
+          <t>GION GOZU（祇園）</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>4202</v>
+        <v>2060</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>課税（内税8%）</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>382</v>
+        <v>152</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3820</v>
+        <v>1908</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T7130001075864</t>
+          <t>お土産（菓子）／手提げ袋のみ10%／登録番号T5160001021611</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026/04/23</t>
+          <t>2026/04/29</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>551蓬莱 ポルタ京都店</t>
+          <t>ワークマン女子 イオンモールKYOTO店</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>970</v>
+        <v>3480</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>71</v>
+        <v>316</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>899</v>
+        <v>3164</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
+          <t>作業着／登録番号T1070001013828</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026/04/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>タリーズコーヒー 祇園花見小路店</t>
+          <t>日本郵便（大津観音寺郵便局）</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>390</v>
+        <v>210</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>355</v>
+        <v>210</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T9011101048118</t>
+          <t>スマートレター（郵便・非課税）／登録番号T1010001112577</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/25</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>京都市交通局</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/05 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>株式会社アルテピアノ</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G49" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>ICカード入金／登録番号T8800020000809</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/26</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>京都伝統産業ミュージアムショップ</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>1056</v>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>課税（外税10%）</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>誰が袖（衣装用・匂い袋）／登録番号T5130001007704</t>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>業務費として／税額印字なし・科目仮</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>東京海上日動火災保険</t>
+          <t>スターバックス なんば御堂筋グランドビル店</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>12100</v>
+        <v>440</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>対象外</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>12100</v>
+        <v>400</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>保険料（コンビニ払込）・非課税</t>
+          <t>飲食（コーヒー）／登録番号T7011001031943</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026/04/29</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -2170,33 +2228,33 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>すき家 浜大津店</t>
+          <t>大衆そば酒場 しのぶ庵 新大阪店</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1070</v>
+        <v>7436</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>課税（外税10%）</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>97</v>
+        <v>676</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>973</v>
+        <v>6760</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>飲食／深夜料70含む／登録番号T2010401093920</t>
+          <t>飲食／登録番号T8120002069808</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026/04/29</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -2206,83 +2264,83 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>GION GOZU（祇園）</t>
+          <t>スターバックス なんば御堂筋グランドビル店</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2060</v>
+        <v>210</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1908</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>お土産（菓子）／手提げ袋のみ10%／登録番号T5160001021611</t>
+          <t>飲食（コーヒー）／登録番号T7011001031943</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/29</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>ワークマン女子 イオンモールKYOTO店</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>3480</v>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>316</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>3164</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>作業着／登録番号T1070001013828</t>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/02</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>中華料理 麒麟（大阪市中央区）</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>10540</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>958</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>9582</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>飲食（中華）／税額印字なし・推定／登録番号T8810205792540</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/05</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>日本郵便（大津観音寺郵便局）</t>
+          <t>JR西日本 大津京駅</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>210</v>
+        <v>5000</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -2293,75 +2351,104 @@
         <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>210</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>スマートレター（郵便・非課税）／登録番号T1010001112577</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/05 ──</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>パンとエスプレッソと嵐山庭園</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>2930</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2714</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>パン・軽食（8%中心／袋のみ10%）／登録番号T4120001146446</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/01</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>株式会社アルテピアノ</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="n">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局 東山</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>業務費として／税額印字なし・科目仮</t>
+      <c r="G56" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/06</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>スターバックス なんば御堂筋グランドビル店</t>
+          <t>DCM 川内店</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>440</v>
+        <v>2777</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -2369,21 +2456,21 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>400</v>
+        <v>2525</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T7011001031943</t>
+          <t>ゴム板・ネジロックカッター／登録番号T7010701039115</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/06</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -2393,69 +2480,69 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>大衆そば酒場 しのぶ庵 新大阪店</t>
+          <t>竈 炊き立てごはん 土井 八条口店</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>7436</v>
+        <v>7700</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>課税（外税10%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>676</v>
+        <v>700</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>6760</v>
+        <v>7000</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T8120002069808</t>
+          <t>飲食／登録番号T8130001006884</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>スターバックス なんば御堂筋グランドビル店</t>
+          <t>アクセスチケット 大阪2ビル店</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>210</v>
+        <v>4980</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>191</v>
+        <v>4980</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T7011001031943</t>
+          <t>金券（阪急阪神優待カード・京阪乗車券）／登録番号T1021001018755</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026/05/02</t>
+          <t>2026/05/07</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -2465,11 +2552,11 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>中華料理 麒麟（大阪市中央区）</t>
+          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>10540</v>
+        <v>4635</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
@@ -2477,57 +2564,57 @@
         </is>
       </c>
       <c r="F60" s="8" t="n">
-        <v>958</v>
+        <v>421</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>9582</v>
+        <v>4213</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>飲食（中華）／税額印字なし・推定／登録番号T8810205792540</t>
+          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026/05/05</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大津京駅</t>
+          <t>居酒屋ひがも（京都市山科区）</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5000</v>
+        <v>5180</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>5000</v>
+        <v>4709</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食代 ※内消費税額の記載なし・概算</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026/05/05</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -2537,249 +2624,237 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>パンとエスプレッソと嵐山庭園</t>
+          <t>串かつ屋 まねき串（京都市山科区）</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2930</v>
+        <v>5100</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>216</v>
+        <v>464</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>2714</v>
+        <v>4636</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>パン・軽食（8%中心／袋のみ10%）／登録番号T4120001146446</t>
+          <t>ご飲食代</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/06</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>京都市交通局 東山</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>楽天市場（セブン払込・イーザッコ米）</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>5670</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮。米（食品）なら軽減8%の可能性</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/06</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>消耗品費</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>DCM 川内店</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>2777</v>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>252</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>2525</v>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>ゴム板・ネジロックカッター／登録番号T7010701039115</t>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Amazon（セブン払込）</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>7590</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>品目不明→科目仮</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026/05/06</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>竈 炊き立てごはん 土井 八条口店</t>
+          <t>京阪電気鉄道（浜大津・手書き）</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T8130001006884</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/05/11</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>浜大津酒場（大津）</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>2354</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>但 飲食代として</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>京都紫明ライオンズクラブ</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>大文字登山アクティビティ 会費として</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>アクセスチケット 大阪2ビル店</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>4980</v>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Agoda（Y's Cabin Osaka Namba）</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>要確認（海外OTA）</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>金券（阪急阪神優待カード・京阪乗車券）／登録番号T1021001018755</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/07</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>421</v>
-      </c>
-      <c r="G67" s="8" t="n">
-        <v>4213</v>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>飲食2名 ※金額要確認（OCRで小計3,584と合計4,635が混在）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/07</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>大衆酒場マルリキ 大阪駅前第2ビル店</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>3584</v>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>325</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>3259</v>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>飲食（居酒屋）</t>
+      <c r="G68" s="8" t="n">
+        <v>1882</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>宿泊1泊／USD11.92</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2789,11 +2864,11 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>居酒屋ひがも（京都市山科区）</t>
+          <t>はちきん（新梅田食道街）</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>5180</v>
+        <v>11540</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -2801,193 +2876,201 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>470</v>
+        <v>1049</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>4709</v>
+        <v>10491</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>飲食代 ※内消費税額の記載なし・概算</t>
+          <t>飲食（居酒屋）／登録番号T5122001015976</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>串かつ屋 まねき串（京都市山科区）</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>5100</v>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>464</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>4636</v>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>ご飲食代</t>
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>ペレ・グレイス（宅急便コレクト・代引）</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税）</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>2736</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>29264</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>品目：美容液・サプリ・書籍／科目仮・要確認</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026/05/09</t>
+          <t>2026/05/16</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>雑費</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>楽天市場（セブン払込・イーザッコ米）</t>
+          <t>PLAGE BARBER SHOP 山科店</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>5670</v>
+        <v>2200</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
+          <t>課税（外税10%）</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>2000</v>
+      </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>品目不明→科目仮。米（食品）なら軽減8%の可能性</t>
+          <t>散髪代（カット）・経費該当要確認／登録番号T7120101032980</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Amazon（セブン払込）</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>7590</v>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="n"/>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮</t>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/17</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>京都市交通局</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>ICカード入金／登録番号T8800020000809</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/09</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>amazon（コンビニ払込・ウェルネット）</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>7590</v>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="n">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="8" t="n">
-        <v>7590</v>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮／インボイスなし</t>
+      <c r="G73" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>京阪電気鉄道（浜大津・手書き）</t>
+          <t>遠京茶寮</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>2000</v>
+        <v>3900</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2000</v>
+        <v>3546</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（コーヒー）／登録番号T1400001155689</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -2997,11 +3080,11 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>浜大津酒場（大津）</t>
+          <t>あびこハウス</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2590</v>
+        <v>1500</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -3009,197 +3092,201 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2354</v>
+        <v>1364</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>但 飲食代として</t>
+          <t>飲食／登録番号T3120001032416</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026/05/12</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>諸会費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>京都紫明ライオンズクラブ</t>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>3000</v>
+      </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>大文字登山アクティビティ 会費として</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Agoda（Y's Cabin Osaka Namba）</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>1882</v>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>要確認（海外OTA）</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="n">
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>JR西日本 大阪駅</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="8" t="n">
-        <v>1882</v>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>宿泊1泊／USD11.92</t>
+      <c r="G77" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/21</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>はちきん（新梅田食道街）</t>
+          <t>JR西日本 大津京駅</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>11540</v>
+        <v>3000</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>1049</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>10491</v>
+        <v>3000</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>飲食（居酒屋）／登録番号T5122001015976</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>ペレ・グレイス（宅急便コレクト・代引）</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税）</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>2736</v>
-      </c>
-      <c r="G79" s="8" t="n">
-        <v>29264</v>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>品目：美容液・サプリ・書籍／科目仮・要確認</t>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Holly's Café 堺筋本町店</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1309</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>飲食（カフェ）／登録番号T4130001010287</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/16</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>雑費</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>PLAGE BARBER SHOP 山科店</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>課税（外税10%）</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>散髪代（カット）・経費該当要確認／登録番号T7120101032980</t>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>ローソン 大津中央二丁目店</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>非課税</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>交通系マネーチャージ</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026/05/17</t>
+          <t>2026/05/24</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -3209,7 +3296,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>京都市交通局</t>
+          <t>JR西日本 大阪駅</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -3228,86 +3315,86 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>ICカード入金／登録番号T8800020000809</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>JR西日本 大阪駅</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>株式会社串まつ屋</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>9020</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>820</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>8200</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>飲食（串カツ）／税額印字なし・推定／登録番号T5120001224663</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>遠京茶寮</t>
+          <t>阪急電鉄 大阪梅田駅</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>3900</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>3546</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T1400001155689</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -3317,11 +3404,11 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>あびこハウス</t>
+          <t>デリカフェ・キッチン大阪</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1500</v>
+        <v>1170</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
@@ -3329,21 +3416,21 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1364</v>
+        <v>1064</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T3120001032416</t>
+          <t>飲食（コーヒー）／登録番号T6120001064803</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -3379,7 +3466,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -3389,11 +3476,11 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大阪駅</t>
+          <t>JR西日本 京都駅</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
@@ -3404,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
@@ -3415,43 +3502,43 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大津京駅</t>
+          <t>梅田大衆酒場H</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>3000</v>
+        <v>2118</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3000</v>
+        <v>1926</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（居酒屋）／登録番号T3120001194454</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -3461,367 +3548,371 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Holly's Café 堺筋本町店</t>
+          <t>東北うまいもの祭り 阪急梅田店（新杵屋）</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1440</v>
+        <v>2090</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>課税（内税8%）</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1309</v>
+        <v>1936</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>飲食（カフェ）／登録番号T4130001010287</t>
+          <t>お土産（食品）／登録番号T8390002012939</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ローソン 大津中央二丁目店</t>
+          <t>どんがめ 大阪駅前第二ビル店</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1000</v>
+        <v>3443</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1000</v>
+        <v>3130</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>交通系マネーチャージ</t>
+          <t>飲食／登録番号T4120001220630</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 大阪駅</t>
+          <t>ZETTERIA ディアモール大阪</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>3000</v>
+        <v>640</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税8%）</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>3000</v>
+        <v>593</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食（テイクアウト）／登録番号T6011101058111</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/24</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>株式会社串まつ屋</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="n">
-        <v>9020</v>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="n">
-        <v>820</v>
-      </c>
-      <c r="G91" s="8" t="n">
-        <v>8200</v>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>飲食（串カツ）／税額印字なし・推定／登録番号T5120001224663</t>
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>551蓬莱 南海新今宮店</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税8%）</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>686</v>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>荷造運賃</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>阪急電鉄 大阪梅田駅</t>
+          <t>ヤマト運輸（宅急便着払）</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1000</v>
+        <v>1530</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1000</v>
+        <v>1391</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>宅急便着払・精密機器（MIZUKENより）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>デリカフェ・キッチン大阪</t>
+          <t>アクセスチケット 大阪2ビル店</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1170</v>
+        <v>3800</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1064</v>
+        <v>3800</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T6120001064803</t>
+          <t>金券（阪急阪神優待カード10回）／登録番号T1021001018755</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+          <t>サイゼリヤ 大阪駅前第3ビル</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>3000</v>
+        <v>637</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>飲食／登録番号T8030001065552</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>JR西日本 京都駅</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>インド家庭料理 マハラジャ</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>4439</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>4035</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>飲食／税額印字なし・推定／登録番号T6120102023261</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>京田辺三山木食堂</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>2950</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>飲食／登録番号T2150003002514</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>消耗品費</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>阪急梅田 2階中央催事</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="n">
-        <v>2090</v>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="9" t="inlineStr">
-        <is>
-          <t>交通系IC支払・品目不明→科目仮</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>南海 新今宮駅店（交通系IC支払）</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="n">
-        <v>740</v>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="8" t="n">
-        <v>740</v>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>品目不明→科目仮</t>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>京都 舞妓の茶本舗</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>課税（外税8%）</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>お茶（徳用ティーバッグ・軽減8%）／登録番号T3130001069770</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>梅田大衆酒場H</t>
+          <t>コンセプト JR三山木駅前第2パーキング</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>2118</v>
+        <v>200</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
@@ -3829,93 +3920,64 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1926</v>
+        <v>182</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>飲食（居酒屋）／登録番号T3120001194454</t>
+          <t>駐車場代／登録番号T2130001023547</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>東北うまいもの祭り 阪急梅田店（新杵屋）</t>
+          <t>京阪電気鉄道 墨染駅</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>2090</v>
+        <v>1000</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1936</v>
+        <v>1000</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>お土産（食品）／登録番号T8390002012939</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>どんがめ 大阪駅前第二ビル店</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="n">
-        <v>3443</v>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>313</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>3130</v>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>飲食／登録番号T4120001220630</t>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/06 ──</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3925,11 +3987,11 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>ZETTERIA ディアモール大阪</t>
+          <t>甘党 御座候（西中島）</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>640</v>
+        <v>550</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -3937,21 +3999,21 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>593</v>
+        <v>510</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>飲食（テイクアウト）／登録番号T6011101058111</t>
+          <t>お土産（御座候・食品）／登録番号T1140001058816</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -3961,69 +4023,69 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>551蓬莱 南海新今宮店</t>
+          <t>タリーズコーヒー 新大阪阪急ビル店</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>740</v>
+        <v>1110</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>686</v>
+        <v>1010</v>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>お土産（豚まん・焼売）／登録番号T4120001089208</t>
+          <t>飲食（コーヒー）／登録番号T9011101048118</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>荷造運賃</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>ヤマト運輸（宅急便着払）</t>
+          <t>JR西日本 新大阪駅</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1530</v>
+        <v>1000</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1391</v>
+        <v>1000</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>宅急便着払・精密機器（MIZUKENより）</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -4033,11 +4095,11 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>アクセスチケット 大阪2ビル店</t>
+          <t>JR西日本 大津駅</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
@@ -4048,32 +4110,32 @@
         <v>0</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>金券（阪急阪神優待カード10回）／登録番号T1021001018755</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>サイゼリヤ 大阪駅前第3ビル</t>
+          <t>セブンイレブン ハートインJR大阪駅西店</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -4081,57 +4143,57 @@
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>637</v>
+        <v>1273</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T8030001065552</t>
+          <t>プリント代／登録番号T6140001055008</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>インド家庭料理 マハラジャ</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>4439</v>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="G106" s="8" t="n">
-        <v>4035</v>
-      </c>
-      <c r="H106" s="9" t="inlineStr">
-        <is>
-          <t>飲食／税額印字なし・推定／登録番号T6120102023261</t>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/03</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>セブンイレブン ハートインJR大阪駅西店</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>プリント代／登録番号T6140001055008</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/03</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -4141,11 +4203,11 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>京田辺三山木食堂</t>
+          <t>スターバックス エキマルシェ大阪店</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>2950</v>
+        <v>394</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -4153,71 +4215,71 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2682</v>
+        <v>359</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>飲食／登録番号T2150003002514</t>
+          <t>交通系IC伝票（同一取引）／登録番号T7011001031943</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>京都 舞妓の茶本舗</t>
+          <t>京都市交通局</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>1080</v>
+        <v>5000</v>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>課税（外税8%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>お茶（徳用ティーバッグ・軽減8%）／登録番号T3130001069770</t>
+          <t>ICカード入金</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>コンセプト JR三山木駅前第2パーキング</t>
+          <t>でんがな 大阪駅前第2ビル店</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>200</v>
+        <v>3931</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -4225,100 +4287,129 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>18</v>
+        <v>357</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>182</v>
+        <v>3574</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>駐車場代／登録番号T2130001023547</t>
+          <t>飲食（居酒屋）／登録番号T1010401049915</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/05</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>酒場 おちょぼ 大阪駅前第3ビル店</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>飲食（居酒屋）／登録番号T2120001110726</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/07</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>京阪電気鉄道 墨染駅</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="n">
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>京阪電気鉄道 びわ湖浜大津駅</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>非課税</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F111" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="5" t="n">
+      <c r="G111" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>ICカードチャージ</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/06 ──</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/07</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>甘党 御座候（西中島）</t>
+          <t>ローソン 浜大津四丁目店</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>550</v>
+        <v>180</v>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%）</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>510</v>
+        <v>164</v>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>お土産（御座候・食品）／登録番号T1140001058816</t>
+          <t>プリント代</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -4328,11 +4419,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>タリーズコーヒー 新大阪阪急ビル店</t>
+          <t>Holly's Café 梅田ダイヒル店</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>1110</v>
+        <v>870</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
@@ -4340,21 +4431,21 @@
         </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1010</v>
+        <v>791</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>飲食（コーヒー）／登録番号T9011101048118</t>
+          <t>飲食（クレジット）。登録番号1413001010267</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/06/08</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -4364,7 +4455,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 新大阪駅</t>
+          <t>大阪メトロ 谷町九丁目駅</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
@@ -4388,45 +4479,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/03</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>JR西日本 大津駅</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>2026/06/08</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>（店名判読不可）お買上票</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>7480</v>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>680</v>
+      </c>
+      <c r="G115" s="8" t="n">
+        <v>6800</v>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>品目・店名不明→科目仮。登録番号T5120001224663</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -4436,11 +4527,11 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>セブンイレブン ハートインJR大阪駅西店</t>
+          <t>ローソン 横浜スカイビル店</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>1400</v>
+        <v>40</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
@@ -4448,57 +4539,57 @@
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>1273</v>
+        <v>37</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>プリント代／登録番号T6140001055008</t>
+          <t>プリント代</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>セブンイレブン ハートインJR大阪駅西店</t>
+          <t>東急電鉄 大井町駅</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>546</v>
+        <v>1000</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>プリント代／登録番号T6140001055008</t>
+          <t>現金チャージ。登録番号T2011001127829</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -4508,11 +4599,11 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>スターバックス エキマルシェ大阪店</t>
+          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>394</v>
+        <v>4048</v>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
@@ -4520,57 +4611,57 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>35</v>
+        <v>368</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>359</v>
+        <v>3680</v>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>交通系IC伝票（同一取引）／登録番号T7011001031943</t>
+          <t>飲食2名。登録番号T9040001029191</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026/06/04</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>京都市交通局</t>
+          <t>山下本気うどん 横浜ポルタ</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>5000</v>
+        <v>1090</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>5000</v>
+        <v>991</v>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>ICカード入金</t>
+          <t>飲食／登録番号T1011101075301</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -4580,263 +4671,201 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>でんがな 大阪駅前第2ビル店</t>
+          <t>大津ハイウエイレストラン（大津SA・GRANVISTA）</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>3931</v>
+        <v>2298</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>課税（内税8%/10%）</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>357</v>
+        <v>179</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>3574</v>
+        <v>2119</v>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>飲食（居酒屋）／登録番号T1010401049915</t>
+          <t>お土産（ちりめん山椒・菓子）／登録番号T2010001093115</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>酒場 おちょぼ 大阪駅前第3ビル店</t>
+          <t>JR西日本 京都駅</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2013</v>
+        <v>1000</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>非課税</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1830</v>
+        <v>1000</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>飲食（居酒屋）／登録番号T2120001110726</t>
+          <t>ICカードチャージ</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026/06/07</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>らーめん小菜 古潭 サン広場店</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>343</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>3437</v>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>飲食（ラーメン）／登録番号T8120001071814</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>京阪電気鉄道 びわ湖浜大津駅</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/07</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>ローソン 浜大津四丁目店</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>プリント代</t>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Agoda（M's Hotel 三条 和国）</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>25428</v>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>要確認（海外OTA）</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="n"/>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Holly's Café 梅田ダイヒル店</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="n">
-        <v>870</v>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>791</v>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>飲食（クレジット）。登録番号1413001010267</t>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>── 2026/05 ──</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>大阪メトロ 谷町九丁目駅</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H125" s="6" t="inlineStr">
-        <is>
-          <t>ICカードチャージ</t>
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/(要確認)</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>大阪信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>課税（内税10%）</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G125" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>2026/06/08</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>（店名判読不可）お買上票</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="n">
-        <v>7480</v>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>680</v>
-      </c>
-      <c r="G126" s="8" t="n">
-        <v>6800</v>
-      </c>
-      <c r="H126" s="9" t="inlineStr">
-        <is>
-          <t>品目・店名不明→科目仮。登録番号T5120001224663</t>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>── 期間外の写真（2026/4より前・要確認：①決算済の可能性） ──</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2025/07/16</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ローソン 横浜スカイビル店</t>
+          <t>Swissotel Nankai Osaka（Swiss Gourmet）</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>40</v>
+        <v>1400</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
@@ -4844,57 +4873,57 @@
         </is>
       </c>
       <c r="F127" s="5" t="n">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>37</v>
+        <v>1273</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>プリント代</t>
+          <t>飲食（コーヒー）／登録番号T3120001104504</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2025/12/15</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>東急電鉄 大井町駅</t>
+          <t>CAFE 英國屋 阪急17番街店</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>1000</v>
+        <v>2730</v>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
+          <t>課税（内税10%）</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>1000</v>
+        <v>2482</v>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>現金チャージ。登録番号T2011001127829</t>
+          <t>飲食（カフェ）／登録番号T8120001080641</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/20</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -4904,11 +4933,11 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Grill&amp;Bar 品川（アトレ品川4F）</t>
+          <t>あびこハウス</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>4048</v>
+        <v>1400</v>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
@@ -4916,652 +4945,415 @@
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>368</v>
+        <v>127</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>3680</v>
+        <v>1273</v>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>飲食2名。登録番号T9040001029191</t>
+          <t>飲食／登録番号T3120001032416</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>山下本気うどん 横浜ポルタ</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="n">
-        <v>1090</v>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="G130" s="5" t="n">
-        <v>991</v>
-      </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>飲食／登録番号T1011101075301</t>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>── 参考：資金移動（経費対象外） ──</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>（資金移動・対象外）</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>大津ハイウエイレストラン（大津SA・GRANVISTA）</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>2298</v>
-      </c>
+          <t>楽天銀行（ATM）</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="n"/>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>課税（内税8%/10%）</t>
+          <t>対象外</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>179</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>2119</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G131" s="4" t="n"/>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>お土産（ちりめん山椒・菓子）／登録番号T2010001093115</t>
+          <t>ATM・金額印字なし</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>2026/06/09</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>atré品川（JRE POINT明細）</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="n">
-        <v>4048</v>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="n">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/25</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G132" s="8" t="n">
-        <v>4048</v>
-      </c>
-      <c r="H132" s="9" t="inlineStr">
-        <is>
-          <t>ポイント明細票・税額印字なし（AW5-5アトレ品川と同一取引の可能性）</t>
+      <c r="G132" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外／手数料110円</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>（資金移動・対象外）</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>JR西日本 京都駅</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="n">
-        <v>1000</v>
-      </c>
+          <t>PayPay銀行 ATM</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="n"/>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>非課税</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>1000</v>
-      </c>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>ICカードチャージ</t>
+          <t>残高36,412／ATM手数料0。経費でない</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>（資金移動・対象外）</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>らーめん小菜 古潭 サン広場店</t>
+          <t>大阪信用金庫（ATM）</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>3780</v>
+        <v>50000</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>課税（内税10%）</t>
+          <t>対象外</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>3437</v>
+        <v>50000</v>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>飲食（ラーメン）／登録番号T8120001071814</t>
+          <t>ATM出金・経費対象外／手数料110円</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>PayPay銀行（ATM）</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>残高照会・金額印字なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（ATM）</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>ATM出金・経費対象外／手数料110円</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/(要確認)</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>（資金移動・対象外）</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>大阪信用金庫 ATM 引出</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="n"/>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>現金引出＝普通預金→現金。経費でない（手数料110は上に計上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>経費 合計（②・要確認分を含む・暫定）</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>458251</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>明細119件（期間外3・重複6を除外済）／黄色＝要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>科目別小計</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="inlineStr">
         <is>
           <t>旅費交通費</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
-        <is>
-          <t>Agoda（M's Hotel 三条 和国）</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="n">
-        <v>25428</v>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>要確認（海外OTA）</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="n"/>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="9" t="inlineStr">
-        <is>
-          <t>宿泊4泊 6/18-6/22。USD158.72建て。消費税区分要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>── 2026/05 ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>2026/05/(要確認)</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>大阪信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D137" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>課税（内税10%）</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G137" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>ATM引出手数料。引出¥50,000は資金移動・対象外。日付要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>── 参考：資金移動（経費対象外） ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/09</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>楽天銀行（ATM）</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="n"/>
-      <c r="G139" s="4" t="n"/>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>ATM・金額印字なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/25</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>京都信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>ATM出金・経費対象外／手数料110円</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/01</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>PayPay銀行 ATM</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>残高36,412／ATM手数料0。経費でない</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/01</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>大阪信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="n"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>ATM出金・経費対象外／手数料110円</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>京都信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>ATM出金・経費対象外</t>
-        </is>
+      <c r="D143" s="12" t="n">
+        <v>177490</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>PayPay銀行（ATM）</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>残高照会・金額印字なし</t>
-        </is>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>会議費・接待費</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="n">
+        <v>168746</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/31</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>京都信用金庫（ATM）</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>ATM出金・経費対象外／手数料110円</t>
-        </is>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>82365</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/(要確認)</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>（資金移動・対象外）</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>大阪信用金庫 ATM 引出</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>現金引出＝普通預金→現金。経費でない（手数料110は上に計上）</t>
-        </is>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>保険料</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>11710</v>
       </c>
     </row>
     <row r="148">
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>経費 合計（要確認分を含む・暫定）</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="n">
-        <v>482983</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>明細128件（重複除去済）／黄色＝要確認。ATM引出等は合計に含めない</t>
-        </is>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>雑費</t>
+        </is>
+      </c>
+      <c r="D148" s="12" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="150">
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>科目別小計</t>
-        </is>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>荷造運賃</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="n">
+        <v>1530</v>
       </c>
     </row>
     <row r="151">
       <c r="C151" t="inlineStr">
         <is>
-          <t>会議費・接待費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D151" s="12" t="n">
-        <v>181908</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="D152" s="12" t="n">
-        <v>177490</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>消耗品費</t>
-        </is>
-      </c>
-      <c r="D153" s="12" t="n">
-        <v>93935</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>保険料</t>
-        </is>
-      </c>
-      <c r="D154" s="12" t="n">
-        <v>12100</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="D155" s="12" t="n">
-        <v>11710</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>雑費</t>
-        </is>
-      </c>
-      <c r="D156" s="12" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>諸会費</t>
-        </is>
-      </c>
-      <c r="D157" s="12" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>荷造運賃</t>
-        </is>
-      </c>
-      <c r="D158" s="12" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D159" s="12" t="n">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A9:H9"/>
+  <mergeCells count="7">
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A124:H124"/>
+    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A130:H130"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A136:H136"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A138:H138"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A126:H126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
